--- a/inventory-wholesale-example.xlsx
+++ b/inventory-wholesale-example.xlsx
@@ -1,41 +1,116 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22827"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\imas-two-api\i-max-pos\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB8C6D84-255E-422A-B0B1-F0C72E76C7C5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+  <si>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t>Product Code</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Buying Price</t>
+  </si>
+  <si>
+    <t>Selling Price</t>
+  </si>
+  <si>
+    <t>Unit of Measure</t>
+  </si>
+  <si>
+    <t>Wholesale Qty 1</t>
+  </si>
+  <si>
+    <t>Wholesale Price 1</t>
+  </si>
+  <si>
+    <t>Wholesale Qty 2</t>
+  </si>
+  <si>
+    <t>Wholesale Price 2</t>
+  </si>
+  <si>
+    <t>Wholesale Qty 3</t>
+  </si>
+  <si>
+    <t>Wholesale Price 3</t>
+  </si>
+  <si>
+    <t>Wholesale Qty 4</t>
+  </si>
+  <si>
+    <t>Wholesale Price 4</t>
+  </si>
+  <si>
+    <t>Cement 50KG</t>
+  </si>
+  <si>
+    <t>CM001</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>bag</t>
+  </si>
+  <si>
+    <t>Brick Red</t>
+  </si>
+  <si>
+    <t>BR001</t>
+  </si>
+  <si>
+    <t>piece</t>
+  </si>
+  <si>
+    <t>Paint White 5Gal</t>
+  </si>
+  <si>
+    <t>PT001</t>
+  </si>
+  <si>
+    <t>Paint</t>
+  </si>
+  <si>
+    <t>liter</t>
+  </si>
+  <si>
+    <t>Steel Rod 12mm</t>
+  </si>
+  <si>
+    <t>SR001</t>
+  </si>
+  <si>
+    <t>Steel</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -72,6 +147,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,62 +479,72 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.5" customWidth="1"/>
+    <col min="2" max="2" width="20.8984375" customWidth="1"/>
+    <col min="3" max="3" width="15.796875" customWidth="1"/>
+    <col min="4" max="4" width="18.69921875" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="22.69921875" customWidth="1"/>
+    <col min="7" max="7" width="13.796875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Product Name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Product Code</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Category</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Buying Price</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Selling Price</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Unit of Measure</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Wholesale Qty 1</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Wholesale Price 1</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Wholesale Qty 2</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Wholesale Price 2</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Wholesale Qty 3</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Wholesale Price 3</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Wholesale Qty 4</v>
-      </c>
-      <c r="N1" t="str">
-        <v>Wholesale Price 4</v>
+    <row r="1" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Cement 50KG</v>
-      </c>
-      <c r="B2" t="str">
-        <v>CM001</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Construction</v>
+    <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
       </c>
       <c r="D2">
         <v>8000</v>
@@ -459,8 +552,8 @@
       <c r="E2">
         <v>15000</v>
       </c>
-      <c r="F2" t="str">
-        <v>bag</v>
+      <c r="F2" t="s">
+        <v>17</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -481,15 +574,15 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Brick Red</v>
-      </c>
-      <c r="B3" t="str">
-        <v>BR001</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Construction</v>
+    <row r="3" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
       </c>
       <c r="D3">
         <v>4000</v>
@@ -497,8 +590,8 @@
       <c r="E3">
         <v>8000</v>
       </c>
-      <c r="F3" t="str">
-        <v>piece</v>
+      <c r="F3" t="s">
+        <v>20</v>
       </c>
       <c r="G3">
         <v>10</v>
@@ -513,15 +606,15 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Paint White 5Gal</v>
-      </c>
-      <c r="B4" t="str">
-        <v>PT001</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Paint</v>
+    <row r="4" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
       </c>
       <c r="D4">
         <v>25000</v>
@@ -529,8 +622,8 @@
       <c r="E4">
         <v>45000</v>
       </c>
-      <c r="F4" t="str">
-        <v>liter</v>
+      <c r="F4" t="s">
+        <v>24</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -557,15 +650,15 @@
         <v>32000</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Steel Rod 12mm</v>
-      </c>
-      <c r="B5" t="str">
-        <v>SR001</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Steel</v>
+    <row r="5" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
       </c>
       <c r="D5">
         <v>35000</v>
@@ -573,13 +666,14 @@
       <c r="E5">
         <v>55000</v>
       </c>
-      <c r="F5" t="str">
-        <v>piece</v>
+      <c r="F5" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N5"/>
+    <ignoredError sqref="A1:N5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>